--- a/Master-Data-Automation/Master_Data_Automation_Scripts/cleaned/cleaned_file_B81LAX_PHASE_1.xlsx
+++ b/Master-Data-Automation/Master_Data_Automation_Scripts/cleaned/cleaned_file_B81LAX_PHASE_1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1-Customers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2-Contacts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3-Sales_reps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4-Sales_Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AR_ARID" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="AR_STATION" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="BASIC CO INFO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DB" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ACCT_IDs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Customers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Contacts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Sales_reps" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Sales_Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR_ARID" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AR_STATION" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BASIC CO INFO" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACCT_IDs" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -852,7 +852,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MINISTRY OF FOREIGN AFFAIRS</t>
+          <t>MINISTRY OF FOREIGN AFFAIRS KWI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TROPEAKA PTY LTD</t>
+          <t>TROPEAKA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MINISTRY OF FOREIGN AFFAIRS</t>
+          <t>MINISTRY OF FOREIGN AFFAIRS SAFAT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1010 PRINTING INTL LTD</t>
+          <t>1010 PRINTING INTERNATIONAL LTD.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010 PRINTING INTERNATIONAL LTD </t>
+          <t>1010 PRINTING INTERNATIONAL LTD.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SEW JOY CREATIONS</t>
+          <t>JOY GALBRAITH/MASTERMIND</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1630,17 +1630,25 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>170000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>170000</v>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1766,7 +1774,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KING STREET PRODS</t>
+          <t>KING STREET JUSTIN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -2184,7 +2192,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>URBAN FIRE CORP % ADCOM WORLWIDE</t>
+          <t>URBAN FIRE CORP</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -2207,7 +2215,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>L7E5T3</t>
+          <t>L7E 5T3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2268,17 +2276,25 @@
       <c r="AI9" t="n">
         <v>19000101</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>150000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>150000</v>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>150000</t>
+        </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -2304,12 +2320,12 @@
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr"/>
@@ -3022,7 +3038,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TCFTV-"ORDINARY JOE"</t>
+          <t>TCFTV-ORD JOE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -3100,17 +3116,25 @@
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>170000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>170000</v>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -3236,7 +3260,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INDIZEN OPTICAL TECH</t>
+          <t>INDIZEN OPTICAL TECHNOLOGIES</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -3442,7 +3466,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BRIGHTSTAR FOX PRDUCTIONS  LLC</t>
+          <t>BRIGHT FILTHY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -3453,7 +3477,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>BRIGHTSTAR FOX PRDUCTIONS  LLC</t>
+          <t>BRIGHTSTAR FOX PRDUCTIONS, LLC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -3724,17 +3748,25 @@
       <c r="AI16" t="n">
         <v>19000101</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>190000</v>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -3860,7 +3892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LAIKA</t>
+          <t>LAIKA - 97124</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -3940,17 +3972,25 @@
       <c r="AI17" t="n">
         <v>19000101</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>190000</v>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -4160,11 +4200,15 @@
       <c r="AI18" t="n">
         <v>20200428</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>170000</v>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
@@ -4292,7 +4336,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RPE PRODS  LLC</t>
+          <t>OUTER RANGE HAYLEY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -4303,7 +4347,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>RPE PRODUCTIONS  LLC</t>
+          <t>RPE PRODUCTIONS, LLC</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -4498,7 +4542,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KING STREET PRODUCIONS</t>
+          <t>KING STREET PRODUCTIONS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -4700,7 +4744,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>STALWART PRODS LLC</t>
+          <t>STALPROD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -5250,7 +5294,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DANIELS ENGRAVING CO  INC</t>
+          <t>DANIEL ENGRAVE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -5261,7 +5305,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DANIELS ENGRAVING CO  INC</t>
+          <t>DANIELS ENGRAVING CO. INC</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -5328,17 +5372,25 @@
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>170000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>170000</v>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -5464,7 +5516,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KING PRODS  INC     1923 SUITE 405</t>
+          <t>KING 1923</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -5475,7 +5527,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>KING PRODUCTIONS  INC  1923 SUITE 405</t>
+          <t>KING PRODUCTIONS, INC. 1923 SUITE 405</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -5670,7 +5722,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>POPCORN PRODS LLC</t>
+          <t>POPCORN PRODUCTIONS, LLC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -6102,7 +6154,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>REAL AMERN HERO</t>
+          <t>REAL AMERICAN/SHEA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -6400,17 +6452,25 @@
       <c r="AI29" t="n">
         <v>20150317</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>190000</v>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -6544,7 +6604,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATL ANTHEM PRODCO  INC    </t>
+          <t>NATIONAL ANTHEM PRODCO, INC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -6555,7 +6615,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NATIONAL ANTHEM PRODCO  INC </t>
+          <t>NATIONAL ANTHEM PRODCO, INC.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -6976,7 +7036,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PHILLIPINE FOODTRADE CORP</t>
+          <t>PHILIPPINE FOODTRADE CORPORATION</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -7054,17 +7114,25 @@
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>160000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>160000</v>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -7198,7 +7266,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PHILIPPINE FOODTRADE CORP</t>
+          <t>PHILLIPINE FOODTRADE CORPORATION</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -7276,17 +7344,25 @@
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>160000</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>80000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>160000</v>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>080000</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -7420,7 +7496,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CONSULATE GEN OF KUWAIT</t>
+          <t>CONSULATE GENERAL OF KUWAIT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -7502,11 +7578,15 @@
       <c r="AI34" t="n">
         <v>20150721</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>170000</v>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
       </c>
       <c r="AL34" t="inlineStr"/>
       <c r="AM34" t="inlineStr"/>
@@ -7726,17 +7806,25 @@
       <c r="AI35" t="n">
         <v>20221022</v>
       </c>
-      <c r="AJ35" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>190000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>90000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>190000</v>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>090000</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>190000</t>
+        </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -7870,7 +7958,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HAUSER AND WIRTH</t>
+          <t>B81 HAUSER</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -8436,7 +8524,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>310-969-3198</t>
+          <t>310 969 3198</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -8492,7 +8580,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -8604,7 +8692,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -8716,7 +8804,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -8824,7 +8912,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -8936,7 +9024,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -9048,7 +9136,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -9160,7 +9248,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -9272,7 +9360,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -9384,7 +9472,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9496,7 +9584,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -9608,7 +9696,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -9720,7 +9808,7 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -9832,7 +9920,7 @@
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -9944,7 +10032,7 @@
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -10056,7 +10144,7 @@
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -10168,7 +10256,7 @@
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -10280,7 +10368,7 @@
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -10392,7 +10480,7 @@
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -10504,7 +10592,7 @@
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -10616,7 +10704,7 @@
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -10728,7 +10816,7 @@
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -10840,7 +10928,7 @@
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -10952,7 +11040,7 @@
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -11064,7 +11152,7 @@
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -11176,7 +11264,7 @@
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -11288,7 +11376,7 @@
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -11400,7 +11488,7 @@
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -11508,7 +11596,7 @@
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -11620,7 +11708,7 @@
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -11732,7 +11820,7 @@
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -11844,7 +11932,7 @@
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -11956,7 +12044,7 @@
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -12068,7 +12156,7 @@
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -12180,7 +12268,7 @@
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -12292,7 +12380,7 @@
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -12404,7 +12492,7 @@
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -12516,7 +12604,7 @@
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -12628,7 +12716,7 @@
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -12740,7 +12828,7 @@
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -12852,7 +12940,7 @@
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -12964,7 +13052,7 @@
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -13068,7 +13156,7 @@
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -13176,7 +13264,7 @@
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -13288,7 +13376,7 @@
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -13400,7 +13488,7 @@
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>C444454</t>
+          <t>B81-C444454</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -13464,12 +13552,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>310-369-4078</t>
+          <t>310 369 4078</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>SEBASTIAN.CAMPOS@FOX.COM</t>
+          <t>sebastian.campos@fox.com</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -13524,7 +13612,7 @@
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>C444455</t>
+          <t>B81-C444455</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -13632,7 +13720,7 @@
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>C444455</t>
+          <t>B81-C444455</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -13744,7 +13832,7 @@
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>C444455</t>
+          <t>B81-C444455</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -13848,7 +13936,7 @@
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>C444455</t>
+          <t>B81-C444455</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -13964,7 +14052,7 @@
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>C444455</t>
+          <t>B81-C444455</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -14080,7 +14168,7 @@
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -14196,7 +14284,7 @@
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -14308,7 +14396,7 @@
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -14424,7 +14512,7 @@
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -14540,7 +14628,7 @@
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -14656,7 +14744,7 @@
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -14772,7 +14860,7 @@
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -14888,7 +14976,7 @@
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>C444458</t>
+          <t>B81-C444458</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -14953,7 +15041,7 @@
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
-          <t>MMATOUSEK@LAIKA.COM</t>
+          <t>mmatousek@laika.com</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -15008,7 +15096,7 @@
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>C444460</t>
+          <t>B81-C444460</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -15112,7 +15200,7 @@
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>C444460</t>
+          <t>B81-C444460</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -15224,7 +15312,7 @@
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>C444460</t>
+          <t>B81-C444460</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -15332,7 +15420,7 @@
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>C444460</t>
+          <t>B81-C444460</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -15440,7 +15528,7 @@
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>C444460</t>
+          <t>B81-C444460</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -15500,7 +15588,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>310-556-0400</t>
+          <t>310 556 0400</t>
         </is>
       </c>
       <c r="S65" t="inlineStr"/>
@@ -15556,7 +15644,7 @@
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -15668,7 +15756,7 @@
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -15772,7 +15860,7 @@
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -15884,7 +15972,7 @@
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -15996,7 +16084,7 @@
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -16108,7 +16196,7 @@
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>C444468</t>
+          <t>B81-C444468</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -16220,7 +16308,7 @@
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>C444471</t>
+          <t>B81-C444471</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -16332,7 +16420,7 @@
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>C444471</t>
+          <t>B81-C444471</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -16392,7 +16480,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>310-606-2069</t>
+          <t>310 606 2069</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -16452,7 +16540,7 @@
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -16556,7 +16644,7 @@
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -16664,7 +16752,7 @@
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -16776,7 +16864,7 @@
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -16888,7 +16976,7 @@
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -17000,7 +17088,7 @@
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -17112,7 +17200,7 @@
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -17224,7 +17312,7 @@
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>C444516</t>
+          <t>B81-C444516</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -17344,7 +17432,7 @@
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>C444570</t>
+          <t>B81-C444570</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -17448,7 +17536,7 @@
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>C444570</t>
+          <t>B81-C444570</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -17560,7 +17648,7 @@
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>C501482</t>
+          <t>B81-C501482</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
@@ -17676,7 +17764,7 @@
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>C535017</t>
+          <t>B81-C535017</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
@@ -17788,7 +17876,7 @@
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>C535017</t>
+          <t>B81-C535017</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
@@ -17900,7 +17988,7 @@
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>C543234</t>
+          <t>B81-C543234</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
@@ -18012,7 +18100,7 @@
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>C551930</t>
+          <t>B81-C551930</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -18124,7 +18212,7 @@
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>C551968</t>
+          <t>B81-C551968</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
@@ -18499,8 +18587,10 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>2</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -18538,7 +18628,7 @@
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>S105</t>
+          <t>B81-S105</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -18606,8 +18696,10 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -18645,7 +18737,7 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>S121</t>
+          <t>B81-S121</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -18713,8 +18805,10 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>2</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -18752,7 +18846,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>S119</t>
+          <t>B81-S119</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -18820,8 +18914,10 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>2</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -18859,7 +18955,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>S124</t>
+          <t>B81-S124</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -18927,8 +19023,10 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>2</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -18966,7 +19064,7 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>S183</t>
+          <t>B81-S183</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -19034,8 +19132,10 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>2</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -19073,7 +19173,7 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>S1192</t>
+          <t>B81-S1192</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -19141,8 +19241,10 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>2</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -19180,7 +19282,7 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>S1193</t>
+          <t>B81-S1193</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -19248,8 +19350,10 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>2</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -19287,7 +19391,7 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>S1382</t>
+          <t>B81-S1382</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -19355,8 +19459,10 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>2</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -19394,7 +19500,7 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>S1037</t>
+          <t>B81-S1037</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -19462,8 +19568,10 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="n">
-        <v>2</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -19501,7 +19609,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>S1381</t>
+          <t>B81-S1381</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -19569,8 +19677,10 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>2</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -19608,7 +19718,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>S282</t>
+          <t>B81-S282</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -19676,8 +19786,10 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>2</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -19715,7 +19827,7 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>S212</t>
+          <t>B81-S212</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
